--- a/RCA_Pocket_Exemplo.xlsx
+++ b/RCA_Pocket_Exemplo.xlsx
@@ -523,7 +523,7 @@
 (+2 mais)</t>
   </si>
   <si>
-    <t xml:space="preserve">Issue Acompanhamento</t>
+    <t xml:space="preserve">S</t>
   </si>
   <si>
     <t xml:space="preserve">Issue Original</t>
